--- a/DataTables/DetailText/剧情/028_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/028_02治疗成功.xlsx
@@ -1,40 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AFD4B4-C417-4155-8187-541BA7DABDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46061E55-2870-4635-925F-246B7E677DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
   <si>
     <t>LineIndex</t>
   </si>
@@ -190,10 +177,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>贵公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>left</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -214,10 +197,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>很多人表面看着正常，其实病得都不轻呢。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -230,7 +209,117 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>胡扯，我看你就是没病说成有病，</t>
+    <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>很多人表面上看着正常，其实都病得不轻呢。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>咱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>家可是花了好多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱，把地都卖了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>供你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读书，就只望着你能出人头地，光宗耀祖。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>可你怎么就</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>么不争气呢？</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>...</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -238,7 +327,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +389,20 @@
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -378,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -465,9 +568,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -678,7 +784,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" customWidth="1"/>
     <col min="2" max="2" width="12.875" customWidth="1"/>
@@ -696,7 +802,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
@@ -758,7 +864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="25" t="s">
         <v>32</v>
       </c>
@@ -1029,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1091,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1103,16 +1209,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1133,7 +1239,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1145,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>10</v>
@@ -1154,7 +1260,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1166,16 +1272,16 @@
         <v>8</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1187,16 +1293,16 @@
         <v>8</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -1208,7 +1314,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>10</v>
@@ -1217,7 +1323,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I8" s="3"/>
     </row>
@@ -1237,8 +1343,8 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="29" t="s">
-        <v>45</v>
+      <c r="H9" s="28" t="s">
+        <v>48</v>
       </c>
       <c r="I9" s="3"/>
     </row>
@@ -1250,16 +1356,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="29" t="s">
-        <v>49</v>
+      <c r="H10" s="28" t="s">
+        <v>47</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -1267,145 +1373,131 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="28" t="s">
+        <v>49</v>
+      </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="28" t="s">
+        <v>50</v>
+      </c>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>37</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="30" t="s">
+        <v>51</v>
+      </c>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="30" t="s">
+        <v>53</v>
+      </c>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="30" t="s">
+        <v>54</v>
+      </c>
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>37</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="30" t="s">
+        <v>42</v>
+      </c>
       <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>